--- a/0.说明文件与教程/支线规划表.xlsx
+++ b/0.说明文件与教程/支线规划表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>注：所有等级区间安排不考虑刷等级
 剧情类支线的难度不必严格对应等级阶段</t>
@@ -170,6 +170,10 @@
   </si>
   <si>
     <t>28——30（67：不败传说的破灭！）</t>
+  </si>
+  <si>
+    <t>67开启：机器价值→信号源
+(机器游荡区+斯巴达副本+密林中央，难度较大，延伸至32级)</t>
   </si>
   <si>
     <t>67开启：挑战全力黑铁</t>
@@ -1506,20 +1510,22 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="O11" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="43.8" customHeight="1" spans="1:17">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -1530,13 +1536,13 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" s="11"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1556,7 +1562,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1576,7 +1582,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1595,9 +1601,10 @@
       <c r="P15" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="O7:O9"/>
+    <mergeCell ref="O11:O12"/>
     <mergeCell ref="Q8:Q9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/0.说明文件与教程/支线规划表.xlsx
+++ b/0.说明文件与教程/支线规划表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>注：所有等级区间安排不考虑刷等级
 剧情类支线的难度不必严格对应等级阶段</t>
@@ -127,6 +127,11 @@
   <si>
     <t>25开启：净水试剂及其效果→
 材料净水的秘密</t>
+  </si>
+  <si>
+    <t>27开启：钉子→交差
+（简单大学城周边+简单堕落城下水道入口）
+难度较高因此延伸到23级</t>
   </si>
   <si>
     <t>19开启：挑战任务→毒死硬化
@@ -365,7 +370,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,6 +386,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -721,7 +732,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -745,16 +756,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -763,89 +774,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -867,28 +878,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1219,7 +1233,7 @@
     <col min="4" max="4" width="32.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="20.7777777777778" customWidth="1"/>
     <col min="6" max="6" width="16.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="11.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="26.8240740740741" customWidth="1"/>
     <col min="11" max="11" width="27.8888888888889" customWidth="1"/>
     <col min="12" max="15" width="28.2222222222222" customWidth="1"/>
     <col min="16" max="16" width="26.5555555555556" customWidth="1"/>
@@ -1349,7 +1363,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
-      <c r="P4" s="8" t="s">
+      <c r="P4" s="9" t="s">
         <v>25</v>
       </c>
       <c r="Q4" s="2"/>
@@ -1373,7 +1387,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="10" t="s">
         <v>28</v>
       </c>
       <c r="Q5" s="2"/>
@@ -1389,7 +1403,9 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="G6" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -1397,64 +1413,64 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="13" t="s">
+      <c r="P6" s="10" t="s">
         <v>32</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="58.2" customHeight="1" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11" t="s">
-        <v>35</v>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="P7" s="2"/>
-      <c r="Q7" s="14" t="s">
-        <v>36</v>
+      <c r="Q7" s="15" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" ht="32.4" customHeight="1" spans="1:17">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="G8" s="7"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="12"/>
       <c r="P8" s="2"/>
-      <c r="Q8" s="14" t="s">
-        <v>38</v>
+      <c r="Q8" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1468,13 +1484,13 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="11"/>
+      <c r="O9" s="12"/>
       <c r="P9" s="2"/>
-      <c r="Q9" s="14"/>
+      <c r="Q9" s="15"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1489,14 +1505,14 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="12" t="s">
-        <v>41</v>
+      <c r="P10" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="Q10" s="2"/>
     </row>
     <row r="11" ht="25.2" customHeight="1" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1510,22 +1526,22 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="11" t="s">
-        <v>43</v>
+      <c r="O11" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="P11" s="2"/>
-      <c r="Q11" s="14" t="s">
-        <v>44</v>
+      <c r="Q11" s="15" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" ht="43.8" customHeight="1" spans="1:17">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="7" t="s">
-        <v>46</v>
+      <c r="D12" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -1536,13 +1552,13 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="11"/>
+      <c r="O12" s="12"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1562,7 +1578,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1582,7 +1598,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1601,8 +1617,9 @@
       <c r="P15" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C1:K1"/>
+    <mergeCell ref="G6:G8"/>
     <mergeCell ref="O7:O9"/>
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="Q8:Q9"/>

--- a/0.说明文件与教程/支线规划表.xlsx
+++ b/0.说明文件与教程/支线规划表.xlsx
@@ -220,7 +220,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -379,7 +378,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFF8B8B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -958,6 +957,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF8B8B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
